--- a/master/result/27_凤临九天_女帝归来/27_凤临九天_女帝归来.xlsx
+++ b/master/result/27_凤临九天_女帝归来/27_凤临九天_女帝归来.xlsx
@@ -397,533 +397,675 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C47"/>
+  <dimension ref="A1:D47"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>rural</v>
       </c>
       <c r="B2" t="str">
-        <v>rural</v>
+        <v>/rural/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>乡村的</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>loaf</v>
       </c>
       <c r="B3" t="str">
-        <v>loaf</v>
+        <v>/loaf/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>一个面包</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>imperial</v>
       </c>
       <c r="B4" t="str">
-        <v>imperial</v>
+        <v>/imperial/</v>
       </c>
       <c r="C4" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>帝国的</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>endure</v>
       </c>
       <c r="B5" t="str">
-        <v>endure</v>
+        <v>/ɪnˈdjʊə/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>忍受</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>portion</v>
       </c>
       <c r="B6" t="str">
+        <v>/portion/</v>
+      </c>
+      <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
+        <v>一份</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>cucumber</v>
+      </c>
+      <c r="B7" t="str">
+        <v>/cucumber/</v>
+      </c>
+      <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
+        <v>黄瓜</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>many</v>
+      </c>
+      <c r="B8" t="str">
+        <v>/many/</v>
+      </c>
+      <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
+        <v>许多</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>boast</v>
+      </c>
+      <c r="B9" t="str">
+        <v>/boast/</v>
+      </c>
+      <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
+        <v>自夸</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>plenty</v>
+      </c>
+      <c r="B10" t="str">
+        <v>/plenty/</v>
+      </c>
+      <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
+        <v>大量</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>worthwhile</v>
+      </c>
+      <c r="B11" t="str">
+        <v>/worthwhile/</v>
+      </c>
+      <c r="C11" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D11" t="str">
+        <v>值得的</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>conquest</v>
+      </c>
+      <c r="B12" t="str">
+        <v>/ˈkɒŋkwest/</v>
+      </c>
+      <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
+        <v>征服</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>fable</v>
+      </c>
+      <c r="B13" t="str">
+        <v>/fable/</v>
+      </c>
+      <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
+        <v>寓言</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>find</v>
+      </c>
+      <c r="B14" t="str">
+        <v>/faɪnd/</v>
+      </c>
+      <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
+        <v>找到</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>badge</v>
+      </c>
+      <c r="B15" t="str">
+        <v>/badge/</v>
+      </c>
+      <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
+        <v>徽章</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>arch</v>
+      </c>
+      <c r="B16" t="str">
+        <v>/arch/</v>
+      </c>
+      <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
+        <v>拱门</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>flash</v>
+      </c>
+      <c r="B17" t="str">
+        <v>/flæʃ/</v>
+      </c>
+      <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>闪光</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>mercury</v>
+      </c>
+      <c r="B18" t="str">
+        <v>/mercury/</v>
+      </c>
+      <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
+        <v>水银</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>skull</v>
+      </c>
+      <c r="B19" t="str">
+        <v>/skull/</v>
+      </c>
+      <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
+        <v>头盖骨</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>gallery</v>
+      </c>
+      <c r="B20" t="str">
+        <v>/gallery/</v>
+      </c>
+      <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
+        <v>画廊</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>saint</v>
+      </c>
+      <c r="B21" t="str">
+        <v>/saint/</v>
+      </c>
+      <c r="C21" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D21" t="str">
+        <v>圣人</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>vain</v>
+      </c>
+      <c r="B22" t="str">
+        <v>/vain/</v>
+      </c>
+      <c r="C22" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D22" t="str">
+        <v>徒劳的</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>gramme</v>
+      </c>
+      <c r="B23" t="str">
+        <v>/gramme/</v>
+      </c>
+      <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
+        <v>克</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>wrench</v>
+      </c>
+      <c r="B24" t="str">
+        <v>/wrench/</v>
+      </c>
+      <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
+        <v>扳手</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>minute</v>
+      </c>
+      <c r="B25" t="str">
+        <v>/minute/</v>
+      </c>
+      <c r="C25" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D25" t="str">
+        <v>分钟</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>impressive</v>
+      </c>
+      <c r="B26" t="str">
+        <v>/impressive/</v>
+      </c>
+      <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
+        <v>给人深刻印象的</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>retail</v>
+      </c>
+      <c r="B27" t="str">
+        <v>/retail/</v>
+      </c>
+      <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
+        <v>零售</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>cashier</v>
+      </c>
+      <c r="B28" t="str">
+        <v>/kæˈʃɪə/</v>
+      </c>
+      <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
+        <v>收银员</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>wage</v>
+      </c>
+      <c r="B29" t="str">
+        <v>/wage/</v>
+      </c>
+      <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
+        <v>工资</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>stationary</v>
+      </c>
+      <c r="B30" t="str">
+        <v>/stationary/</v>
+      </c>
+      <c r="C30" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D30" t="str">
+        <v>静止的</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>offset</v>
+      </c>
+      <c r="B31" t="str">
+        <v>/offset/</v>
+      </c>
+      <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
+        <v>抵消</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>vase</v>
+      </c>
+      <c r="B32" t="str">
+        <v>/vase/</v>
+      </c>
+      <c r="C32" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D32" t="str">
+        <v>花瓶</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>catalog</v>
+      </c>
+      <c r="B33" t="str">
+        <v>/catalog/</v>
+      </c>
+      <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
+        <v>目录</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>editorial</v>
+      </c>
+      <c r="B34" t="str">
+        <v>/editorial/</v>
+      </c>
+      <c r="C34" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D34" t="str">
+        <v>社论</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
         <v>portion</v>
       </c>
-      <c r="C6" t="str">
-        <v>一份</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="str">
-        <v>cucumber</v>
-      </c>
-      <c r="C7" t="str">
-        <v>黄瓜</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="str">
-        <v>many</v>
-      </c>
-      <c r="C8" t="str">
-        <v>许多</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="str">
-        <v>boast</v>
-      </c>
-      <c r="C9" t="str">
-        <v>自夸</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="str">
-        <v>plenty</v>
-      </c>
-      <c r="C10" t="str">
-        <v>大量</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>worthwhile</v>
-      </c>
-      <c r="C11" t="str">
-        <v>值得的</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>conquest</v>
-      </c>
-      <c r="C12" t="str">
-        <v>征服</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>fable</v>
-      </c>
-      <c r="C13" t="str">
-        <v>寓言</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="str">
-        <v>find</v>
-      </c>
-      <c r="C14" t="str">
-        <v>找到</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="str">
-        <v>badge</v>
-      </c>
-      <c r="C15" t="str">
-        <v>徽章</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="str">
-        <v>arch</v>
-      </c>
-      <c r="C16" t="str">
-        <v>拱门</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="str">
-        <v>flash</v>
-      </c>
-      <c r="C17" t="str">
-        <v>闪光</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="str">
-        <v>mercury</v>
-      </c>
-      <c r="C18" t="str">
-        <v>水银</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="str">
-        <v>skull</v>
-      </c>
-      <c r="C19" t="str">
-        <v>头盖骨</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="str">
-        <v>gallery</v>
-      </c>
-      <c r="C20" t="str">
-        <v>画廊</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="str">
-        <v>saint</v>
-      </c>
-      <c r="C21" t="str">
-        <v>圣人</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="str">
-        <v>vain</v>
-      </c>
-      <c r="C22" t="str">
-        <v>徒劳的</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="str">
-        <v>gramme</v>
-      </c>
-      <c r="C23" t="str">
-        <v>克</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="str">
-        <v>wrench</v>
-      </c>
-      <c r="C24" t="str">
-        <v>扳手</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" t="str">
-        <v>minute</v>
-      </c>
-      <c r="C25" t="str">
-        <v>分钟</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="str">
-        <v>impressive</v>
-      </c>
-      <c r="C26" t="str">
-        <v>给人深刻印象的</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="str">
-        <v>retail</v>
-      </c>
-      <c r="C27" t="str">
-        <v>零售</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28" t="str">
-        <v>cashier</v>
-      </c>
-      <c r="C28" t="str">
-        <v>收银员</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29" t="str">
-        <v>wage</v>
-      </c>
-      <c r="C29" t="str">
-        <v>工资</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30" t="str">
-        <v>stationary</v>
-      </c>
-      <c r="C30" t="str">
-        <v>静止的</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31" t="str">
-        <v>offset</v>
-      </c>
-      <c r="C31" t="str">
-        <v>抵消</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="str">
-        <v>vase</v>
-      </c>
-      <c r="C32" t="str">
-        <v>花瓶</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="str">
-        <v>catalog</v>
-      </c>
-      <c r="C33" t="str">
-        <v>目录</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="str">
-        <v>editorial</v>
-      </c>
-      <c r="C34" t="str">
-        <v>社论</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
       <c r="B35" t="str">
-        <v>portion</v>
+        <v>/portion/</v>
       </c>
       <c r="C35" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>一部分</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>prohibit</v>
       </c>
       <c r="B36" t="str">
-        <v>prohibit</v>
+        <v>/prohibit/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>禁止</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>long</v>
       </c>
       <c r="B37" t="str">
-        <v>long</v>
+        <v>/long/</v>
       </c>
       <c r="C37" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D37" t="str">
         <v>长的</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>reasonable</v>
       </c>
       <c r="B38" t="str">
-        <v>reasonable</v>
+        <v>/reasonable/</v>
       </c>
       <c r="C38" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>合理的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>ambulance</v>
       </c>
       <c r="B39" t="str">
-        <v>ambulance</v>
+        <v>/ˈæmbjʊləns/</v>
       </c>
       <c r="C39" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>救护车</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>nervous</v>
       </c>
       <c r="B40" t="str">
-        <v>nervous</v>
+        <v>/nervous/</v>
       </c>
       <c r="C40" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D40" t="str">
         <v>紧张的</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>tune</v>
       </c>
       <c r="B41" t="str">
-        <v>tune</v>
+        <v>/tune/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>曲调</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>baby</v>
       </c>
       <c r="B42" t="str">
-        <v>baby</v>
+        <v>/baby/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>婴儿</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>migrate</v>
       </c>
       <c r="B43" t="str">
-        <v>migrate</v>
+        <v>/migrate/</v>
       </c>
       <c r="C43" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D43" t="str">
         <v>迁移</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>compose</v>
       </c>
       <c r="B44" t="str">
-        <v>compose</v>
+        <v>/compose/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>创作</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>lure</v>
       </c>
       <c r="B45" t="str">
-        <v>lure</v>
+        <v>/lure/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>吸引力</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>litre</v>
       </c>
       <c r="B46" t="str">
-        <v>litre</v>
+        <v>/litre/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>升</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>temper</v>
       </c>
       <c r="B47" t="str">
-        <v>temper</v>
+        <v>/temper/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>脾气</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D47"/>
   </ignoredErrors>
 </worksheet>
 </file>